--- a/data/P2/P2T3_BQ5.xlsx
+++ b/data/P2/P2T3_BQ5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BB3691-CBB8-C648-99C9-C3D7EFFF6AD3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DC705F-503F-FE41-B418-9668B9417F9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30140" yWindow="2400" windowWidth="27000" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28600" yWindow="1440" windowWidth="33580" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="164">
   <si>
     <t>word</t>
   </si>
@@ -550,6 +550,100 @@
   <si>
     <t>syllable</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orders we must follow at school or home</t>
+  </si>
+  <si>
+    <t>Tidy dirty things and put rubbish away</t>
+  </si>
+  <si>
+    <t>Speak and act nicely to other people</t>
+  </si>
+  <si>
+    <t>A person who draws, paints or makes art works</t>
+  </si>
+  <si>
+    <t>The head teacher of a whole school</t>
+  </si>
+  <si>
+    <t>A person who helps people borrow books in library</t>
+  </si>
+  <si>
+    <t>A person who cooks tasty food in restaurants</t>
+  </si>
+  <si>
+    <t>A person who helps sick people get well</t>
+  </si>
+  <si>
+    <t>A doctor who looks after our teeth</t>
+  </si>
+  <si>
+    <t>A person who flies airplanes</t>
+  </si>
+  <si>
+    <t>A person who keeps everyone safe</t>
+  </si>
+  <si>
+    <t>A person who helps doctors look after sick people</t>
+  </si>
+  <si>
+    <t>A doctor that treats sick animals</t>
+  </si>
+  <si>
+    <t>A person who puts out fires and saves people</t>
+  </si>
+  <si>
+    <t>A person who sells things in shops</t>
+  </si>
+  <si>
+    <t>A person who studies nature and does experiments</t>
+  </si>
+  <si>
+    <t>A person who cuts and styles people’s hair</t>
+  </si>
+  <si>
+    <t>A person who brings food to guests in restaurants</t>
+  </si>
+  <si>
+    <t>A place at school to eat lunch</t>
+  </si>
+  <si>
+    <t>A safe road line for people to walk across streets</t>
+  </si>
+  <si>
+    <t>Hit a door gently before you go in</t>
+  </si>
+  <si>
+    <t>Take something quickly with your hand</t>
+  </si>
+  <si>
+    <t>Give something to another person</t>
+  </si>
+  <si>
+    <t>Ask someone to join your activity or party</t>
+  </si>
+  <si>
+    <t>Let others use your toys or food together</t>
+  </si>
+  <si>
+    <t>Do things one after another, not all at once</t>
+  </si>
+  <si>
+    <t>Stand in a straight line and wait</t>
+  </si>
+  <si>
+    <t>Listen and follow rules well</t>
+  </si>
+  <si>
+    <t>Think about how other people feel</t>
+  </si>
+  <si>
+    <t>Kind and care about other people’s needs</t>
   </si>
 </sst>
 </file>
@@ -984,11 +1078,12 @@
   <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" thickBot="1">
@@ -1007,6 +1102,11 @@
       <c r="E1" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:12" ht="27" thickBot="1">
       <c r="A2" s="1" t="s">
@@ -1024,7 +1124,9 @@
       <c r="E2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="F2" t="s">
+        <v>134</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
@@ -1044,6 +1146,9 @@
       <c r="E3" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="F3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="27" thickBot="1">
       <c r="A4" s="1" t="s">
@@ -1061,6 +1166,9 @@
       <c r="E4" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="F4" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="27" thickBot="1">
       <c r="A5" s="1" t="s">
@@ -1078,6 +1186,9 @@
       <c r="E5" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="F5" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="27" thickBot="1">
       <c r="A6" s="1" t="s">
@@ -1095,6 +1206,9 @@
       <c r="E6" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="F6" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="27" thickBot="1">
       <c r="A7" s="1" t="s">
@@ -1112,7 +1226,9 @@
       <c r="E7" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="F7" t="s">
+        <v>139</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
@@ -1132,6 +1248,9 @@
       <c r="E8" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F8" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="27" thickBot="1">
       <c r="A9" s="1" t="s">
@@ -1149,6 +1268,9 @@
       <c r="E9" s="6" t="s">
         <v>90</v>
       </c>
+      <c r="F9" t="s">
+        <v>141</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -1169,6 +1291,9 @@
       <c r="E10" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="F10" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="27" thickBot="1">
       <c r="A11" s="1" t="s">
@@ -1186,6 +1311,9 @@
       <c r="E11" s="6" t="s">
         <v>97</v>
       </c>
+      <c r="F11" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="27" thickBot="1">
       <c r="A12" s="1" t="s">
@@ -1203,6 +1331,9 @@
       <c r="E12" s="6" t="s">
         <v>99</v>
       </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="27" thickBot="1">
       <c r="A13" s="1" t="s">
@@ -1220,6 +1351,9 @@
       <c r="E13" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F13" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="27" thickBot="1">
       <c r="A14" s="1" t="s">
@@ -1237,6 +1371,9 @@
       <c r="E14" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F14" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="27" thickBot="1">
       <c r="A15" s="1" t="s">
@@ -1254,6 +1391,9 @@
       <c r="E15" s="6" t="s">
         <v>103</v>
       </c>
+      <c r="F15" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="27" thickBot="1">
       <c r="A16" s="1" t="s">
@@ -1271,6 +1411,9 @@
       <c r="E16" s="6" t="s">
         <v>105</v>
       </c>
+      <c r="F16" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="27" thickBot="1">
       <c r="A17" s="1" t="s">
@@ -1288,6 +1431,9 @@
       <c r="E17" s="6" t="s">
         <v>113</v>
       </c>
+      <c r="F17" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="27" thickBot="1">
       <c r="A18" s="1" t="s">
@@ -1305,6 +1451,9 @@
       <c r="E18" s="6" t="s">
         <v>107</v>
       </c>
+      <c r="F18" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="49" thickBot="1">
       <c r="A19" s="1" t="s">
@@ -1322,6 +1471,9 @@
       <c r="E19" s="6" t="s">
         <v>111</v>
       </c>
+      <c r="F19" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="27" thickBot="1">
       <c r="A20" s="1" t="s">
@@ -1339,6 +1491,9 @@
       <c r="E20" s="6" t="s">
         <v>109</v>
       </c>
+      <c r="F20" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="27" thickBot="1">
       <c r="A21" s="1" t="s">
@@ -1356,8 +1511,9 @@
       <c r="E21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="F21" t="s">
+        <v>153</v>
+      </c>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" ht="27" thickBot="1">
@@ -1376,6 +1532,9 @@
       <c r="E22" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F22" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="27" thickBot="1">
       <c r="A23" s="1" t="s">
@@ -1393,6 +1552,9 @@
       <c r="E23" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F23" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="24" spans="1:10" ht="27" thickBot="1">
       <c r="A24" s="1" t="s">
@@ -1410,6 +1572,9 @@
       <c r="E24" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F24" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="27" thickBot="1">
       <c r="A25" s="1" t="s">
@@ -1427,6 +1592,9 @@
       <c r="E25" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="F25" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="27" thickBot="1">
       <c r="A26" s="1" t="s">
@@ -1444,6 +1612,9 @@
       <c r="E26" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F26" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="27" thickBot="1">
       <c r="A27" s="1" t="s">
@@ -1461,6 +1632,9 @@
       <c r="E27" s="6" t="s">
         <v>123</v>
       </c>
+      <c r="F27" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="27" thickBot="1">
       <c r="A28" s="1" t="s">
@@ -1478,6 +1652,9 @@
       <c r="E28" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="F28" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="49" thickBot="1">
       <c r="A29" s="1" t="s">
@@ -1495,6 +1672,9 @@
       <c r="E29" s="6" t="s">
         <v>127</v>
       </c>
+      <c r="F29" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="49" thickBot="1">
       <c r="A30" s="1" t="s">
@@ -1512,6 +1692,9 @@
       <c r="E30" s="6" t="s">
         <v>129</v>
       </c>
+      <c r="F30" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="31" spans="1:10" ht="49" thickBot="1">
       <c r="A31" s="1" t="s">
@@ -1528,6 +1711,9 @@
       </c>
       <c r="E31" s="6" t="s">
         <v>131</v>
+      </c>
+      <c r="F31" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
